--- a/out/LSTM-S4_repeat_3_000007.xlsx
+++ b/out/LSTM-S4_repeat_3_000007.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002758331248746254</v>
+        <v>-6.350885619758629e-05</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.179948550397682</v>
+        <v>0.7321632397323752</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.36481272737295</v>
+        <v>1.46545842325624</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4768474474787338</v>
+        <v>0.1097911438137972</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.13429118900086</v>
+        <v>0.9518947012812844</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5962144654737817</v>
+        <v>0.1372747102358227</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.849948467372729</v>
+        <v>1.116670368164936</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8546706087681964</v>
+        <v>0.1967826461112384</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.963411901833958</v>
+        <v>1.373038420346467</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9143282584114923</v>
+        <v>0.2105184526747808</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.93746190391996</v>
+        <v>1.597307351345162</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9690036625202518</v>
+        <v>0.2231063901292494</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.961210938303176</v>
+        <v>1.833019085469454</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4372933306146131</v>
+        <v>0.1006837643598522</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.865988554834539</v>
+        <v>1.811094679552205</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2111926915211731</v>
+        <v>0.04862565627917254</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.305762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.850737664069165</v>
+        <v>1.807583232453053</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.100627642798713</v>
+        <v>0.02316867753908389</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.840631254522454</v>
+        <v>1.805256255114777</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02981526863639063</v>
+        <v>0.006862180623952113</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.799526961544359</v>
+        <v>1.795788932819602</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01972168837616457</v>
+        <v>0.004536897260261469</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.80913950188337</v>
+        <v>1.797998640916994</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01009136346000095</v>
+        <v>0.002320085942499</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.809588785945999</v>
+        <v>1.798098252506395</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005160183427308522</v>
+        <v>0.00118386798434055</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.809810798765857</v>
+        <v>1.79814552668101</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00193640981257436</v>
+        <v>0.0004423189860551449</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.8085202791337</v>
+        <v>1.79784438854966</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001053482668822787</v>
+        <v>0.0002383767632912877</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.80868899584704</v>
+        <v>1.797879399410737</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005044218983078885</v>
+        <v>0.0001126200326826326</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.808644482886998</v>
+        <v>1.797865283292404</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003108495926966479</v>
+        <v>6.781267869019299e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.808760726861537</v>
+        <v>1.797888233616753</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001596990651976723</v>
+        <v>3.308665882696171e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.808770121883489</v>
+        <v>1.797886551950965</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.492745046281422e-05</v>
+        <v>1.29836763541332e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.808760144297121</v>
+        <v>1.797880408501921</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.616585511050847e-05</v>
+        <v>6.512317399864405e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.808777793760443</v>
+        <v>1.797880721933198</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>8.280563881834207e-07</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.808768104905035</v>
+        <v>1.797874578137222</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>-2.941261685029097e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.808760227858122</v>
+        <v>1.797868893603194</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-3.887371769088796e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.808756138045633</v>
+        <v>1.79786414232798</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-4.031182895915095e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.808750270602949</v>
+        <v>1.797858853180418</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.053889915940302e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.80874520124758</v>
+        <v>1.797858830446117</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.808740836273612</v>
+        <v>1.797859148726333</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.905762781659078</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.808741927520068</v>
+        <v>1.797860239972791</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.808741237912932</v>
+        <v>1.797859550365655</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.808741268225335</v>
+        <v>1.797859580678056</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.808741078772824</v>
+        <v>1.797859391225546</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.808741131819527</v>
+        <v>1.797859444272249</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.808741184866229</v>
+        <v>1.797859497318952</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.808741146975728</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.808741018148022</v>
+        <v>1.797859330600743</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.808740874164114</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.808740768070709</v>
+        <v>1.79785908052343</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.808740533149597</v>
+        <v>1.797858845602318</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.808740699867806</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.808740896898415</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.808740737758307</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.808740775648809</v>
+        <v>1.79785908810153</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.808740972679419</v>
+        <v>1.797859285132141</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.808740949945118</v>
+        <v>1.79785926239784</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.808740798383109</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.808740722602106</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.808740821117411</v>
+        <v>1.797859133570133</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.808740828695512</v>
+        <v>1.797859141148233</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.808741093929024</v>
+        <v>1.797859406381747</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.808740798383109</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.808741040882323</v>
+        <v>1.797859353335044</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.808741124241426</v>
+        <v>1.797859436694148</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.808740957523217</v>
+        <v>1.79785926997594</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.808741146975728</v>
+        <v>1.79785945942845</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.808740798383109</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.808740593774399</v>
+        <v>1.797858906227121</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.808740707445905</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.808740722602106</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.808740487680994</v>
+        <v>1.797858800133715</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.808740548305797</v>
+        <v>1.797858860758518</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.808740419478091</v>
+        <v>1.797858731930812</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.808740555883897</v>
+        <v>1.797858868336619</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.808740730180205</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.808740874164114</v>
+        <v>1.797859186616836</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.808740707445905</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.808740699867806</v>
+        <v>1.797859012320526</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.80874041189999</v>
+        <v>1.797858724352711</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.80874042705619</v>
+        <v>1.797858739508913</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.808740654399204</v>
+        <v>1.797858966851924</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.808740639243001</v>
+        <v>1.797858951695724</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.808740745336408</v>
+        <v>1.797859057789129</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.808740472524792</v>
+        <v>1.797858784977515</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.808740571040097</v>
+        <v>1.79785888349282</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.808740722602106</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.808740737758307</v>
+        <v>1.797859050211029</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.808740798383109</v>
+        <v>1.797859110835832</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.808740896898415</v>
+        <v>1.797859209351137</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.808740730180205</v>
+        <v>1.797859042632928</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.808740684711603</v>
+        <v>1.797858997164326</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.808740669555403</v>
+        <v>1.797858982008125</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.808740707445905</v>
+        <v>1.797859019898627</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.808740722602106</v>
+        <v>1.797859035054828</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.808740715024006</v>
+        <v>1.797859027476727</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000007.xlsx
+++ b/out/LSTM-S4_repeat_3_000007.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.905762781659078</v>
+        <v>1.179279226522314</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>2.905762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>2.305762781659078</v>
+        <v>1.946808764566225</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,10 +31949,10 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002758331248746254</v>
+        <v>-0.0002332083449757192</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>3.179948550397682</v>
+        <v>2.688547715269946</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32744,10 +32744,10 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC40" t="n">
-        <v>6.36481272737295</v>
+        <v>5.38125159166431</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4768474474787338</v>
+        <v>0.4031597456031778</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33539,10 +33539,10 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC41" t="n">
-        <v>4.13429118900086</v>
+        <v>3.495414815239047</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5962144654737817</v>
+        <v>0.5040808049610619</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34334,10 +34334,10 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.849948467372729</v>
+        <v>4.10048081771359</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.8546706087681964</v>
+        <v>0.722597443358037</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.963411901833958</v>
+        <v>5.041879586764681</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.9143282584114923</v>
+        <v>0.7730361324468378</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC44" t="n">
-        <v>6.93746190391996</v>
+        <v>5.865408655193725</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.9690036625202518</v>
+        <v>0.8192632254913454</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC45" t="n">
-        <v>7.961210938303176</v>
+        <v>6.730956773298637</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.4372933306146131</v>
+        <v>0.3697175905094338</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>2.305762781659078</v>
+        <v>1.746808764566225</v>
       </c>
       <c r="JC46" t="n">
-        <v>7.865988554834539</v>
+        <v>6.650449257076223</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.2111926915211731</v>
+        <v>0.1785573408662108</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>2.305762781659078</v>
+        <v>0.9792792265223138</v>
       </c>
       <c r="JC47" t="n">
-        <v>7.850737664069165</v>
+        <v>6.637555106419117</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.100627642798713</v>
+        <v>0.08507725693231345</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.2117496884784028</v>
       </c>
       <c r="JC48" t="n">
-        <v>7.840631254522454</v>
+        <v>6.629010480133984</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02981526863639063</v>
+        <v>0.02520779777539015</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC49" t="n">
-        <v>7.799526961544359</v>
+        <v>6.594258195399325</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01972168837616457</v>
+        <v>0.01667353773887012</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC50" t="n">
-        <v>7.80913950188337</v>
+        <v>6.602385272761708</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.01009136346000095</v>
+        <v>0.00853179459886641</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC51" t="n">
-        <v>7.809588785945999</v>
+        <v>6.60276436508064</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.005160183427308522</v>
+        <v>0.004361900352302547</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC52" t="n">
-        <v>7.809810798765857</v>
+        <v>6.602951292894428</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.00193640981257436</v>
+        <v>0.001636683385369897</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC53" t="n">
-        <v>7.8085202791337</v>
+        <v>6.601859450919981</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.001053482668822787</v>
+        <v>0.0008893064793483251</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC54" t="n">
-        <v>7.80868899584704</v>
+        <v>6.602001291466815</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0005044218983078885</v>
+        <v>0.000425743633202614</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC55" t="n">
-        <v>7.808644482886998</v>
+        <v>6.60196287645079</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003108495926966479</v>
+        <v>0.0002616518368248959</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC56" t="n">
-        <v>7.808760726861537</v>
+        <v>6.602060424523549</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001596990651976723</v>
+        <v>0.0001349942054180214</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC57" t="n">
-        <v>7.808770121883489</v>
+        <v>6.602067621643897</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>7.492745046281422e-05</v>
+        <v>6.293833289339209e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC58" t="n">
-        <v>7.808760144297121</v>
+        <v>6.602058416461025</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>4.616585511050847e-05</v>
+        <v>3.849097684393219e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC59" t="n">
-        <v>7.808777793760443</v>
+        <v>6.602072430173592</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.831222555273368e-05</v>
+        <v>1.481539171982363e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC60" t="n">
-        <v>7.808768104905035</v>
+        <v>6.602063541267274</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>5.293691574854516e-06</v>
+        <v>3.234953259883613e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC61" t="n">
-        <v>7.808760227858122</v>
+        <v>6.602056212348583</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>5.63141154556023e-07</v>
+        <v>-5.494870763551826e-07</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC62" t="n">
-        <v>7.808756138045633</v>
+        <v>6.602051957170413</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-2.093548687745288e-06</v>
+        <v>-3.062365791830193e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC63" t="n">
-        <v>7.808750270602949</v>
+        <v>6.602046234891382</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC64" t="n">
-        <v>7.80874520124758</v>
+        <v>6.602041165536013</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.052178947283033</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC65" t="n">
-        <v>7.808740836273612</v>
+        <v>6.602036800562044</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>2.905762781659078</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC66" t="n">
-        <v>7.808741927520068</v>
+        <v>6.602037891808502</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.4521789472830329</v>
+        <v>0.4117496884784029</v>
       </c>
       <c r="JC67" t="n">
-        <v>7.808741237912932</v>
+        <v>6.602037202201365</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.4521789472830329</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC68" t="n">
-        <v>7.808741268225335</v>
+        <v>6.602037232513768</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.3557798495655082</v>
       </c>
       <c r="JC69" t="n">
-        <v>7.808741078772824</v>
+        <v>6.602037043061257</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC70" t="n">
-        <v>7.808741131819527</v>
+        <v>6.602037096107961</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC71" t="n">
-        <v>7.808741184866229</v>
+        <v>6.602037149154663</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC72" t="n">
-        <v>7.808741146975728</v>
+        <v>6.602037111264161</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC73" t="n">
-        <v>7.808741018148022</v>
+        <v>6.602036982436454</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC74" t="n">
-        <v>7.808740874164114</v>
+        <v>6.602036838452547</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC75" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC76" t="n">
-        <v>7.808740768070709</v>
+        <v>6.602036732359141</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC77" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC78" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC79" t="n">
-        <v>7.808740533149597</v>
+        <v>6.602036497438029</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC80" t="n">
-        <v>7.808740699867806</v>
+        <v>6.602036664156238</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC81" t="n">
-        <v>7.808740896898415</v>
+        <v>6.602036861186848</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC82" t="n">
-        <v>7.808740737758307</v>
+        <v>6.60203670204674</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC83" t="n">
-        <v>7.808740775648809</v>
+        <v>6.602036739937241</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC84" t="n">
-        <v>7.808740972679419</v>
+        <v>6.602036936967852</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC85" t="n">
-        <v>7.808740949945118</v>
+        <v>6.60203691423355</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC86" t="n">
-        <v>7.808740798383109</v>
+        <v>6.602036762671542</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC87" t="n">
-        <v>7.808740722602106</v>
+        <v>6.602036686890539</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC88" t="n">
-        <v>7.808740821117411</v>
+        <v>6.602036785405844</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC89" t="n">
-        <v>7.808740828695512</v>
+        <v>6.602036792983944</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC90" t="n">
-        <v>7.808741093929024</v>
+        <v>6.602037058217459</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC91" t="n">
-        <v>7.808740798383109</v>
+        <v>6.602036762671542</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC92" t="n">
-        <v>7.808741040882323</v>
+        <v>6.602037005170755</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC93" t="n">
-        <v>7.808741124241426</v>
+        <v>6.60203708852986</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC94" t="n">
-        <v>7.808740957523217</v>
+        <v>6.602036921811651</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC95" t="n">
-        <v>7.808741146975728</v>
+        <v>6.602037111264161</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC96" t="n">
-        <v>7.808740798383109</v>
+        <v>6.602036762671542</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC97" t="n">
-        <v>7.808740593774399</v>
+        <v>6.602036558062832</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC98" t="n">
-        <v>7.808740707445905</v>
+        <v>6.602036671734338</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC99" t="n">
-        <v>7.808740722602106</v>
+        <v>6.602036686890539</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC100" t="n">
-        <v>7.808740487680994</v>
+        <v>6.602036451969427</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC101" t="n">
-        <v>7.808740548305797</v>
+        <v>6.602036512594229</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC102" t="n">
-        <v>7.808740419478091</v>
+        <v>6.602036383766523</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC103" t="n">
-        <v>7.808740555883897</v>
+        <v>6.60203652017233</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC104" t="n">
-        <v>7.808740730180205</v>
+        <v>6.602036694468639</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC105" t="n">
-        <v>7.808740874164114</v>
+        <v>6.602036838452547</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC106" t="n">
-        <v>7.808740707445905</v>
+        <v>6.602036671734338</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC107" t="n">
-        <v>7.808740699867806</v>
+        <v>6.602036664156238</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC108" t="n">
-        <v>7.80874041189999</v>
+        <v>6.602036376188423</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC109" t="n">
-        <v>7.80874042705619</v>
+        <v>6.602036391344623</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC110" t="n">
-        <v>7.808740654399204</v>
+        <v>6.602036618687635</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC111" t="n">
-        <v>7.808740639243001</v>
+        <v>6.602036603531435</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC112" t="n">
-        <v>7.808740745336408</v>
+        <v>6.60203670962484</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC113" t="n">
-        <v>7.808740472524792</v>
+        <v>6.602036436813226</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC114" t="n">
-        <v>7.808740571040097</v>
+        <v>6.602036535328531</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC115" t="n">
-        <v>7.808740722602106</v>
+        <v>6.602036686890539</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC116" t="n">
-        <v>7.808740737758307</v>
+        <v>6.60203670204674</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC117" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC118" t="n">
-        <v>7.808740798383109</v>
+        <v>6.602036762671542</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC119" t="n">
-        <v>7.808740896898415</v>
+        <v>6.602036861186848</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC120" t="n">
-        <v>7.808740730180205</v>
+        <v>6.602036694468639</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC121" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC122" t="n">
-        <v>7.808740684711603</v>
+        <v>6.602036649000037</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC123" t="n">
-        <v>7.808740669555403</v>
+        <v>6.602036633843836</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC124" t="n">
-        <v>7.808740707445905</v>
+        <v>6.602036671734338</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC125" t="n">
-        <v>7.808740722602106</v>
+        <v>6.602036686890539</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.052178947283033</v>
+        <v>-0.5557798495655083</v>
       </c>
       <c r="JC126" t="n">
-        <v>7.808740715024006</v>
+        <v>6.602036679312438</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_3_000007.xlsx
+++ b/out/LSTM-S4_repeat_3_000007.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006467204540967941</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.004154246300458908</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.003120902925729752</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001894492655992508</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001624863594770432</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.001585166901350021</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001701943576335907</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001680359244346619</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.001502230763435364</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.001330308616161346</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.001225706189870834</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.00104169175028801</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.0006635747849941254</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.0004185400903224945</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.0003699176013469696</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.000585455447435379</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.0005810894072055817</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.0005323663353919983</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.0002764426171779633</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>7.028132677078247e-05</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.179279226522314</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.0005205236375331879</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.946808764566225</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001200739294290543</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.946808764566225</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001238163560628891</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.946808764566225</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001072406768798828</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.946808764566225</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0007962659001350403</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.000502757728099823</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.0004537440836429596</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.0008803047239780426</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.946808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001380406320095062</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.946808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.001501832157373428</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.746808764566225</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001481093466281891</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.746808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001269754022359848</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001188486814498901</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001357272267341614</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001804597675800323</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.003459904342889786</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003425449132919312</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.746808764566225</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,13 +31946,13 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002833958715200424</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.746808764566225</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
-        <v>-0.0002332083449757192</v>
+        <v>-0.0001655819800505415</v>
       </c>
     </row>
     <row r="40">
@@ -32733,7 +32733,7 @@
         <v>0</v>
       </c>
       <c r="IY40" t="n">
-        <v>2.688547715269946</v>
+        <v>1.908915605419707</v>
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
@@ -32741,13 +32741,13 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.00227876752614975</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.746808764566225</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
-        <v>5.38125159166431</v>
+        <v>3.820782201421234</v>
       </c>
     </row>
     <row r="41">
@@ -33528,7 +33528,7 @@
         <v>0</v>
       </c>
       <c r="IY41" t="n">
-        <v>0.4031597456031778</v>
+        <v>0.2862504102768729</v>
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
@@ -33536,13 +33536,13 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001637257635593414</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC41" t="n">
-        <v>3.495414815239047</v>
+        <v>2.481805283148065</v>
       </c>
     </row>
     <row r="42">
@@ -34323,7 +34323,7 @@
         <v>0</v>
       </c>
       <c r="IY42" t="n">
-        <v>0.5040808049610619</v>
+        <v>0.3579062094468367</v>
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
@@ -34331,13 +34331,13 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.0009946525096893311</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.16</v>
       </c>
       <c r="JC42" t="n">
-        <v>4.10048081771359</v>
+        <v>2.911412704952789</v>
       </c>
     </row>
     <row r="43">
@@ -35118,7 +35118,7 @@
         <v>0</v>
       </c>
       <c r="IY43" t="n">
-        <v>0.722597443358037</v>
+        <v>0.5130568539070393</v>
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001389283686876297</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.16</v>
       </c>
       <c r="JC43" t="n">
-        <v>5.041879586764681</v>
+        <v>3.579822185635244</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.7730361324468378</v>
+        <v>0.5488688594293036</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.002083085477352142</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC44" t="n">
-        <v>5.865408655193725</v>
+        <v>4.164541999836108</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.8192632254913454</v>
+        <v>0.5816910990992846</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002773720771074295</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.16</v>
       </c>
       <c r="JC45" t="n">
-        <v>6.730956773298637</v>
+        <v>4.779096175439199</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.3697175905094338</v>
+        <v>0.2625057084191442</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.003164086490869522</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.746808764566225</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>6.650449257076223</v>
+        <v>4.721934442921425</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.1785573408662108</v>
+        <v>0.1267789021009197</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0009248629212379456</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.9792792265223138</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>6.637555106419117</v>
+        <v>4.712779365589396</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.08507725693231345</v>
+        <v>0.06040575950735491</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0003564357757568359</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.2117496884784028</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>6.629010480133984</v>
+        <v>4.706712529200177</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.02520779777539015</v>
+        <v>0.01789816837695915</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.002236109226942062</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>6.594258195399325</v>
+        <v>4.682037535803007</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.01667353773887012</v>
+        <v>0.01183757656008916</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.003240663558244705</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>6.602385272761708</v>
+        <v>4.687806569566344</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00853179459886641</v>
+        <v>0.006056163523399848</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.004028148949146271</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>6.60276436508064</v>
+        <v>4.688074276883612</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.004361900352302547</v>
+        <v>0.003095519383377557</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.004133529961109161</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>6.602951292894428</v>
+        <v>4.68820554651627</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.001636683385369897</v>
+        <v>0.001160602772461799</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.003857351839542389</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>6.601859450919981</v>
+        <v>4.687428883703615</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0008893064793483251</v>
+        <v>0.0006302546024891238</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003627780824899673</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>6.602001291466815</v>
+        <v>4.687528140811389</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.000425743633202614</v>
+        <v>0.0003009710309649564</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.003442544490098953</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>6.60196287645079</v>
+        <v>4.687499426584645</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0002616518368248959</v>
+        <v>0.0001839193825475277</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.00326358899474144</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>6.602060424523549</v>
+        <v>4.687567135797627</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001349942054180214</v>
+        <v>9.381943911860337e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003891915082931519</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>6.602067621643897</v>
+        <v>4.68757079099824</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.293833289339209e-05</v>
+        <v>4.295647027768853e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.001875445246696472</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>6.602058416461025</v>
+        <v>4.687562792321457</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.849097684393219e-05</v>
+        <v>2.569951306630508e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001908861100673676</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>6.602072430173592</v>
+        <v>4.687571494155336</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>1.481539171982363e-05</v>
+        <v>8.987335331640211e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.003569543361663818</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>6.602063541267274</v>
+        <v>4.687563635373489</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>3.234953259883613e-06</v>
+        <v>1.176214944912711e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004852026700973511</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>6.602056212348583</v>
+        <v>4.687556854583018</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-5.494870763551826e-07</v>
+        <v>-1.662115307266386e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.005453072488307953</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>6.602051957170413</v>
+        <v>4.687552434039168</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.005594968795776367</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>6.602046234891382</v>
+        <v>4.687546855744045</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00497455894947052</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>6.602041165536013</v>
+        <v>4.687541809122977</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>-3.735991635587426e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002952024340629578</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.16</v>
       </c>
       <c r="JC65" t="n">
-        <v>6.602036800562044</v>
+        <v>4.687542127403193</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>6.945058703422546e-05</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC66" t="n">
-        <v>6.602037891808502</v>
+        <v>4.68754321864965</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0007289797067642212</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.4117496884784029</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>6.602037202201365</v>
+        <v>4.687542529042514</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003321636468172073</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3557798495655082</v>
+        <v>0.16</v>
       </c>
       <c r="JC68" t="n">
-        <v>6.602037232513768</v>
+        <v>4.687542559354916</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.00594242662191391</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.3557798495655082</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>6.602037043061257</v>
+        <v>4.687542369902406</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.007875289767980576</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>6.602037096107961</v>
+        <v>4.687542422949109</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008979380130767822</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>6.602037149154663</v>
+        <v>4.687542475995811</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009208802133798599</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>6.602037111264161</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.008709851652383804</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>6.602036982436454</v>
+        <v>4.687542309277602</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.008063040673732758</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>6.602036838452547</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.007366165518760681</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006699316203594208</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>6.602036732359141</v>
+        <v>4.68754205920029</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00687369704246521</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.006964001804590225</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.006653476506471634</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>6.602036497438029</v>
+        <v>4.687541824279178</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.006281837821006775</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>6.602036664156238</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.006485875695943832</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>6.602036861186848</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.006737686693668365</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>6.60203670204674</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.006266720592975616</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>6.602036739937241</v>
+        <v>4.68754206677839</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.005577839910984039</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>6.602036936967852</v>
+        <v>4.687542263809</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.005764812231063843</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>6.60203691423355</v>
+        <v>4.687542241074699</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.006386138498783112</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>6.602036762671542</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.006872385740280151</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>6.602036686890539</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.007033653557300568</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>6.602036785405844</v>
+        <v>4.687542112246993</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.00646987184882164</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>6.602036792983944</v>
+        <v>4.687542119825094</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006289292126893997</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>6.602037058217459</v>
+        <v>4.687542385058607</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.006368767470121384</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.16</v>
       </c>
       <c r="JC91" t="n">
-        <v>6.602036762671542</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.005783494561910629</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>6.602037005170755</v>
+        <v>4.687542332011904</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.005757365375757217</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>6.60203708852986</v>
+        <v>4.687542415371008</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.004539553076028824</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>6.602036921811651</v>
+        <v>4.6875422486528</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.00460626557469368</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>6.602037111264161</v>
+        <v>4.687542438105309</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005339913070201874</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>6.602036762671542</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.006154906004667282</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>6.602036558062832</v>
+        <v>4.687541884903981</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.006470758467912674</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>6.602036671734338</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.00607878714799881</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC99" t="n">
-        <v>6.602036686890539</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005631137639284134</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC100" t="n">
-        <v>6.602036451969427</v>
+        <v>4.687541778810576</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.005305510014295578</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>6.602036512594229</v>
+        <v>4.687541839435378</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.00485549122095108</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>6.602036383766523</v>
+        <v>4.687541710607671</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.003538988530635834</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>6.60203652017233</v>
+        <v>4.687541847013479</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.003326792269945145</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>6.602036694468639</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.003873758018016815</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>6.602036838452547</v>
+        <v>4.687542165293696</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.004215523600578308</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>6.602036671734338</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.004615996032953262</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>6.602036664156238</v>
+        <v>4.687541990997386</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.00527665764093399</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC108" t="n">
-        <v>6.602036376188423</v>
+        <v>4.687541703029571</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.005387123674154282</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC109" t="n">
-        <v>6.602036391344623</v>
+        <v>4.687541718185773</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.005293462425470352</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.3</v>
       </c>
       <c r="JC110" t="n">
-        <v>6.602036618687635</v>
+        <v>4.687541945528784</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.004943747073411942</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>6.602036603531435</v>
+        <v>4.687541930372583</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004925400018692017</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.5557798495655083</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
-        <v>6.60203670962484</v>
+        <v>4.687542036465988</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.004811707884073257</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>6.602036436813226</v>
+        <v>4.687541763654375</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.004380010068416595</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>6.602036535328531</v>
+        <v>4.687541862169679</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003896698355674744</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>6.602036686890539</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003676995635032654</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>6.60203670204674</v>
+        <v>4.687542028887888</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003458008170127869</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003196828067302704</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>6.602036762671542</v>
+        <v>4.687542089512691</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003278344869613647</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>6.602036861186848</v>
+        <v>4.687542188027996</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003219690173864365</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>6.602036694468639</v>
+        <v>4.687542021309787</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003000248223543167</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.002867173403501511</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>6.602036649000037</v>
+        <v>4.687541975841185</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.002776436507701874</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>6.602036633843836</v>
+        <v>4.687541960684985</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002828408032655716</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>6.602036671734338</v>
+        <v>4.687541998575486</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002711795270442963</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>6.602036686890539</v>
+        <v>4.687542013731687</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002513501793146133</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.5557798495655083</v>
+        <v>0.3999999999999995</v>
       </c>
       <c r="JC126" t="n">
-        <v>6.602036679312438</v>
+        <v>4.687542006153588</v>
       </c>
     </row>
   </sheetData>
